--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,158 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>230100</v>
+      </c>
+      <c r="E8" s="3">
         <v>234100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>236900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>226000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>214400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>217600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>225200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>219400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>191500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>194300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>197100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>175500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>162000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>155800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>101900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>155300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>158300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,8 +871,11 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,47 +1081,50 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1113,19 +1132,22 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>193300</v>
+      </c>
+      <c r="E17" s="3">
         <v>191000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>184300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>180400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>175800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>174700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>170800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>154800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>338200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>128600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3">
         <v>131300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E18" s="3">
         <v>43100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>52600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>45600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>42900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>54400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>39500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-141100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>24000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,126 +1376,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-17600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-14200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-16800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E21" s="3">
         <v>42300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>51500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>48700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>61400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>59400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>47300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-142300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>45300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>18200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1489,99 +1528,105 @@
         <v>700</v>
       </c>
       <c r="K22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="L22" s="3">
         <v>500</v>
       </c>
       <c r="M22" s="3">
+        <v>500</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E23" s="3">
         <v>24000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>43800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-154900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3">
         <v>6800</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1589,58 +1634,61 @@
         <v>4500</v>
       </c>
       <c r="E24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F24" s="3">
         <v>7200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-44600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>16200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E26" s="3">
         <v>19500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>35700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-110300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3">
         <v>8900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E27" s="3">
         <v>19500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>35700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>35500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-110300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3">
         <v>8900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E32" s="3">
         <v>18400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>17600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>14200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>16800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E33" s="3">
         <v>19500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>35700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>35500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-110300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3">
         <v>8900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E35" s="3">
         <v>19500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>35700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>35500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-110300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3">
         <v>8900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,47 +2483,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E41" s="3">
         <v>62100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>65200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>70300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>162200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>155000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>135300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2457,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,47 +2605,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E43" s="3">
         <v>20800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2575,47 +2667,50 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E44" s="3">
         <v>9200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2634,47 +2729,50 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E45" s="3">
         <v>13100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2693,47 +2791,50 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E46" s="3">
         <v>105300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>181500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>104000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>112500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>101200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>58800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>190000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>157100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2752,8 +2853,11 @@
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,47 +2915,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1558700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1490500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1409500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1373200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1337600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1277800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1249000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1204600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1191000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1000000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>975700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>953200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2870,47 +2977,50 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1252400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1254800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1230400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1231900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1233400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1232900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1228100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1188800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1190000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>884300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>881200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>862600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2929,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,47 +3163,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E52" s="3">
         <v>9000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3106,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,47 +3287,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2881500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2859700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2830600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2717300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2686200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2631500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2561000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2502900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2448100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2079600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2043500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1977600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3224,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,47 +3399,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E57" s="3">
         <v>34800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>25600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3329,8 +3459,11 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3347,7 +3480,7 @@
         <v>700</v>
       </c>
       <c r="H58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>600</v>
@@ -3359,7 +3492,7 @@
         <v>600</v>
       </c>
       <c r="L58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="M58" s="3">
         <v>8900</v>
@@ -3367,8 +3500,8 @@
       <c r="N58" s="3">
         <v>8900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>8900</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
@@ -3388,47 +3521,50 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E59" s="3">
         <v>139400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>150300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>122600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>128200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>113600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>109700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>107200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>102300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>101200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>105200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>95700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3447,47 +3583,50 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>169600</v>
+      </c>
+      <c r="E60" s="3">
         <v>174900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>187100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>153600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>154500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>141800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>135900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>141700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>130200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>136800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>138300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>121900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3506,47 +3645,50 @@
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>911500</v>
+      </c>
+      <c r="E61" s="3">
         <v>911300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>911000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>910800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>910600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>910400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>910200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>909800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>911700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>617200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>619300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1068800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3565,47 +3707,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>885500</v>
+      </c>
+      <c r="E62" s="3">
         <v>880800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>867100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>824200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>820000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>803700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>767500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>750000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>749000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>717300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>711900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>745200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3624,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,47 +3955,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1966500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1967000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1965200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1888600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1885100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1855900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1813600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1801500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1791000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1471400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1469500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1936000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3860,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,47 +4289,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>94600</v>
+      </c>
+      <c r="E72" s="3">
         <v>82200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-27300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-62900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-134700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-162100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-51800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4178,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,47 +4537,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>915000</v>
+      </c>
+      <c r="E76" s="3">
         <v>892700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>865400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>828700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>801100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>775600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>747400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>701400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>657200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>608200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>574000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4414,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E81" s="3">
         <v>19500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>35700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>35500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-110300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3">
         <v>8900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,47 +4816,48 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E83" s="3">
         <v>17600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
@@ -4678,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,47 +5186,50 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E89" s="3">
         <v>48400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>67000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>43700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>50800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>81500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>68100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
@@ -5032,8 +5248,11 @@
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,47 +5274,48 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-109400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-72100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5114,8 +5334,11 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,47 +5458,50 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-123400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-63200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-89800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-453400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5291,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,47 +5792,50 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>290700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5609,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,47 +5916,50 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-74000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>37200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-32700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>50600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-142600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
@@ -5725,6 +5976,9 @@
         <v>4</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,164 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>239200</v>
+      </c>
+      <c r="E8" s="3">
         <v>230100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>234100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>236900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>226000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>214400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>217600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>225200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>219400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>191500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>194300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>197100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>175500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>162000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>155800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>101900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>155300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>158300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,8 +881,11 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,50 +1101,53 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <v>100</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>3300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1135,19 +1155,22 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>198500</v>
+      </c>
+      <c r="E17" s="3">
         <v>193300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>191000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>184300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>180400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>175800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>174700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>170800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>144500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>154800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>338200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>128600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="3">
         <v>131300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E18" s="3">
         <v>36800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>52600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>42900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>51900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>47000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>39500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-141100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>24000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,132 +1410,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-14200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-16800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E21" s="3">
         <v>36200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>40700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>48700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>61400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>59400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>47300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-142300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>45300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>18200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1531,164 +1571,173 @@
         <v>700</v>
       </c>
       <c r="L22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>500</v>
       </c>
       <c r="N22" s="3">
+        <v>500</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E23" s="3">
         <v>16900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>45600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>43800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-154900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T23" s="3">
         <v>6800</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4500</v>
+        <v>9200</v>
       </c>
       <c r="E24" s="3">
         <v>4500</v>
       </c>
       <c r="F24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G24" s="3">
         <v>7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-44600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E26" s="3">
         <v>12400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>35500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>36300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T26" s="3">
         <v>8900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E27" s="3">
         <v>12400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>35700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>35500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-110300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T27" s="3">
         <v>8900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E32" s="3">
         <v>19200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>14200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>16800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E33" s="3">
         <v>12400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>35700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-110300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T33" s="3">
         <v>8900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E35" s="3">
         <v>12400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>35700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-110300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T35" s="3">
         <v>8900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,50 +2570,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E41" s="3">
         <v>19000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>62100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>136100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>65200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>70300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>162200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>155000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2546,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,50 +2698,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E43" s="3">
         <v>21000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2670,50 +2763,53 @@
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E44" s="3">
         <v>9000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2732,50 +2828,53 @@
       <c r="V44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E45" s="3">
         <v>11900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2794,50 +2893,53 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E46" s="3">
         <v>60900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>105300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>181500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>104000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>112500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>75800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>101200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>58800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>190000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>181400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>157100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2856,8 +2958,11 @@
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2918,50 +3023,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1609800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1558700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1490500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1409500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1373200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1337600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1277800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1249000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1204600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1191000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1000000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>975700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>953200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2980,50 +3088,53 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1250800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1252400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1254800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1230400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1231900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1233400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1232900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1228100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1188800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1190000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>884300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>881200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>862600</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,50 +3283,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,50 +3413,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2925300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2881500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2859700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2830600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2717300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2686200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2631500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2561000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2502900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2448100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2079600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2043500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1977600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,50 +3530,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E57" s="3">
         <v>33600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>25600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>26700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3462,13 +3593,16 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>7700</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
@@ -3483,7 +3617,7 @@
         <v>700</v>
       </c>
       <c r="I58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
@@ -3495,7 +3629,7 @@
         <v>600</v>
       </c>
       <c r="M58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>8900</v>
@@ -3503,8 +3637,8 @@
       <c r="O58" s="3">
         <v>8900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+      <c r="P58" s="3">
+        <v>8900</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
@@ -3524,50 +3658,53 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E59" s="3">
         <v>135200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>139400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>150300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>122600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>128200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>113600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>109700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>107200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>102300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>101200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>105200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3586,50 +3723,53 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E60" s="3">
         <v>169600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>187100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>153600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>154500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>141800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>135900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>141700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>130200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>136800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>138300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>121900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3648,50 +3788,53 @@
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>927200</v>
+      </c>
+      <c r="E61" s="3">
         <v>911500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>911300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>911000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>910800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>910600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>910400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>910200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>909800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>911700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>617200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>619300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1068800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3710,50 +3853,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>894700</v>
+      </c>
+      <c r="E62" s="3">
         <v>885500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>880800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>867100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>824200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>820000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>803700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>767500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>750000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>749000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>717300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>711900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>745200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,50 +4113,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1996500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1966500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1967000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1965200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1888600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1885100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1855900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1813600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1801500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1791000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1471400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1469500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1936000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,50 +4463,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E72" s="3">
         <v>94600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>62700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-27300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-62900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-134700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-162100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-51800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,50 +4723,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>928700</v>
+      </c>
+      <c r="E76" s="3">
         <v>915000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>892700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>865400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>828700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>801100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>775600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>747400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>701400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>657200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>608200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>574000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E81" s="3">
         <v>12400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>35700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-110300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T81" s="3">
         <v>8900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,50 +5015,51 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E83" s="3">
         <v>18600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11700</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,50 +5403,53 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E89" s="3">
         <v>39200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>48400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>67000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>43700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>81500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
@@ -5251,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,50 +5495,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-109400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-72100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32300</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,50 +5688,53 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-85700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-123400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-63200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-89800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-453400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28700</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,50 +6038,53 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>290700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5919,50 +6168,53 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-43100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-74000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>66300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-32700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>50600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-142600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
@@ -5979,6 +6231,9 @@
         <v>4</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>255000</v>
+      </c>
+      <c r="E8" s="3">
         <v>239200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>230100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>234100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>236900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>226000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>214400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>217600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>225200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>219400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>191500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>194300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>197100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>175500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>162000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>155800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>101900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>155300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>158300</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,53 +1121,56 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>100</v>
       </c>
       <c r="K14" s="3">
+        <v>100</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>3300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1158,19 +1178,22 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E17" s="3">
         <v>198500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>193300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>191000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>184300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>180400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>175800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>174700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>170800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>167500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>144500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>154800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>338200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>128600</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17" s="3">
         <v>131300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E18" s="3">
         <v>40700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>36800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>43100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>52600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>38600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>42900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-141100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46900</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>24000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,143 +1444,150 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-19200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-18400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-17100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>-16800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E21" s="3">
         <v>46100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>42300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>51500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>45800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>61400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>59400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-142300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>18200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
@@ -1574,170 +1614,179 @@
         <v>700</v>
       </c>
       <c r="M22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>500</v>
       </c>
       <c r="O22" s="3">
+        <v>500</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E23" s="3">
         <v>25800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>24000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>43800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-154900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U23" s="3">
         <v>6800</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E24" s="3">
         <v>9200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>4500</v>
       </c>
       <c r="F24" s="3">
         <v>4500</v>
       </c>
       <c r="G24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="H24" s="3">
         <v>7200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-44600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E26" s="3">
         <v>16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>35700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>36300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-110300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U26" s="3">
         <v>8900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E27" s="3">
         <v>16600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>35700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-110300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U27" s="3">
         <v>8900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E32" s="3">
         <v>14200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>19200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>18400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>17100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>16800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E33" s="3">
         <v>16600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-110300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U33" s="3">
         <v>8900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E35" s="3">
         <v>16600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-110300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U35" s="3">
         <v>8900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,53 +2657,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E41" s="3">
         <v>10700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>62100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>162200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>155000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>135300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,53 +2791,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E43" s="3">
         <v>24200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2766,53 +2859,56 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E44" s="3">
         <v>7600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2831,53 +2927,56 @@
       <c r="W44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E45" s="3">
         <v>10200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2896,53 +2995,56 @@
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E46" s="3">
         <v>52700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>105300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>181500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>104000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>112500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>101200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>58800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>190000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>181400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>157100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2961,8 +3063,11 @@
       <c r="W46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3026,53 +3131,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1661000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1609800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1558700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1490500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1409500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1373200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1337600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1277800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1249000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1204600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1191000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1000000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>975700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>953200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3091,53 +3199,56 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1249100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1250800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1252400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1254800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1230400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1231900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1233400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1232900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1228100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1188800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1190000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>884300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>881200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>862600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,53 +3403,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E52" s="3">
         <v>12000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,53 +3539,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2973100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2925300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2881500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2859700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2830600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2717300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2686200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2631500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2561000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2502900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2448100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2079600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2043500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1977600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,53 +3661,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E57" s="3">
         <v>33700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3596,16 +3727,19 @@
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>700</v>
       </c>
       <c r="F58" s="3">
         <v>700</v>
@@ -3620,7 +3754,7 @@
         <v>700</v>
       </c>
       <c r="J58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>600</v>
@@ -3632,7 +3766,7 @@
         <v>600</v>
       </c>
       <c r="N58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="O58" s="3">
         <v>8900</v>
@@ -3640,8 +3774,8 @@
       <c r="P58" s="3">
         <v>8900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>8900</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
@@ -3661,53 +3795,56 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E59" s="3">
         <v>133300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>135200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>139400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>150300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>122600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>128200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>113600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>109700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>107200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>101200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>105200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>95700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3726,53 +3863,56 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E60" s="3">
         <v>174700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>169600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>187100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>153600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>154500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>141800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>135900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>141700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>130200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>136800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>138300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>121900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3791,53 +3931,56 @@
       <c r="W60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>932900</v>
+      </c>
+      <c r="E61" s="3">
         <v>927200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>911500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>911300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>911000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>910800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>910600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>910400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>910200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>909800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>911700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>617200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>619300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1068800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3856,53 +3999,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>910900</v>
+      </c>
+      <c r="E62" s="3">
         <v>894700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>885500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>880800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>867100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>824200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>820000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>803700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>767500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>750000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>749000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>717300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>711900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>745200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4271,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2023700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1996500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1966500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1967000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1965200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1888600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1885100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1855900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1813600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1801500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1791000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1471400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1469500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1936000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E72" s="3">
         <v>111200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>94600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>82200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>62700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>35600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-62900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-98400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-134700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-162100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-51800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,53 +4909,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>949400</v>
+      </c>
+      <c r="E76" s="3">
         <v>928700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>915000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>892700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>865400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>828700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>801100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>775600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>747400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>701400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>657200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>608200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>574000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E81" s="3">
         <v>16600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-110300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U81" s="3">
         <v>8900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,53 +5214,54 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E83" s="3">
         <v>19600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,53 +5620,56 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E89" s="3">
         <v>58000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>48400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>50100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>67000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>43700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>50800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>53100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>81500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,53 +5716,54 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-109400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-90800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-72100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-30000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,53 +5918,56 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-67700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-76900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-123400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-63200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-56300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-89800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-453400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,53 +6284,56 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>10700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>290700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
@@ -6106,8 +6352,11 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,53 +6420,56 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-43100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-74000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-32700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>50600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-142600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
@@ -6234,6 +6486,9 @@
         <v>4</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,201 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E8" s="3">
         <v>255000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>239200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>230100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>234100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>236900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>226000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>214400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>217600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>225200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>219400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>191500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>194300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>197100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>175500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>162000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>155800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>101900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>155300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>158300</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>172700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>169500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>161200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>167100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>160300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>159000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>149600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -894,31 +901,34 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>85600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>78000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>63000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>73800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>77800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>76400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,56 +1141,59 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="E14" s="3">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G14" s="3">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="J14" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="3">
         <v>100</v>
       </c>
       <c r="L14" s="3">
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1181,42 +1201,45 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>21200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>17300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>200000</v>
+        <v>201700</v>
       </c>
       <c r="E17" s="3">
-        <v>198500</v>
+        <v>197100</v>
       </c>
       <c r="F17" s="3">
-        <v>193300</v>
+        <v>198200</v>
       </c>
       <c r="G17" s="3">
-        <v>191000</v>
+        <v>189700</v>
       </c>
       <c r="H17" s="3">
-        <v>184300</v>
+        <v>189500</v>
       </c>
       <c r="I17" s="3">
+        <v>189000</v>
+      </c>
+      <c r="J17" s="3">
         <v>180400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>175800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>174700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>170800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>144500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>154800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>338200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>128600</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="3">
         <v>131300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>55000</v>
+        <v>47700</v>
       </c>
       <c r="E18" s="3">
-        <v>40700</v>
+        <v>57900</v>
       </c>
       <c r="F18" s="3">
-        <v>36800</v>
+        <v>41000</v>
       </c>
       <c r="G18" s="3">
-        <v>43100</v>
+        <v>40500</v>
       </c>
       <c r="H18" s="3">
-        <v>52600</v>
+        <v>44600</v>
       </c>
       <c r="I18" s="3">
-        <v>45600</v>
+        <v>47900</v>
       </c>
       <c r="J18" s="3">
+        <v>45500</v>
+      </c>
+      <c r="K18" s="3">
         <v>38600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>42900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>54400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>51900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>39500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-141100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>24000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,167 +1478,174 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-19600</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-14200</v>
       </c>
-      <c r="F20" s="3">
-        <v>-19200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-17600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-16800</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>55600</v>
+        <v>68900</v>
       </c>
       <c r="E21" s="3">
-        <v>46100</v>
+        <v>78200</v>
       </c>
       <c r="F21" s="3">
-        <v>36200</v>
+        <v>65800</v>
       </c>
       <c r="G21" s="3">
-        <v>42300</v>
+        <v>59000</v>
       </c>
       <c r="H21" s="3">
-        <v>51500</v>
+        <v>62200</v>
       </c>
       <c r="I21" s="3">
-        <v>45800</v>
+        <v>64400</v>
       </c>
       <c r="J21" s="3">
+        <v>62800</v>
+      </c>
+      <c r="K21" s="3">
         <v>40700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>59400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>18200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>600</v>
+        <v>20700</v>
       </c>
       <c r="E22" s="3">
-        <v>700</v>
+        <v>20300</v>
       </c>
       <c r="F22" s="3">
-        <v>700</v>
+        <v>20000</v>
       </c>
       <c r="G22" s="3">
-        <v>700</v>
+        <v>20000</v>
       </c>
       <c r="H22" s="3">
-        <v>700</v>
+        <v>19100</v>
       </c>
       <c r="I22" s="3">
-        <v>700</v>
+        <v>18300</v>
       </c>
       <c r="J22" s="3">
-        <v>700</v>
+        <v>17700</v>
       </c>
       <c r="K22" s="3">
         <v>700</v>
@@ -1617,176 +1657,185 @@
         <v>700</v>
       </c>
       <c r="N22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
       </c>
       <c r="P22" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E23" s="3">
         <v>34700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>27800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-154900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V23" s="3">
         <v>6800</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E24" s="3">
         <v>12700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>4500</v>
       </c>
       <c r="G24" s="3">
         <v>4500</v>
       </c>
       <c r="H24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I24" s="3">
         <v>7200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E26" s="3">
         <v>22100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>36300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="3">
         <v>8900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E27" s="3">
         <v>22100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="3">
         <v>8900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>19600</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>14200</v>
       </c>
-      <c r="F32" s="3">
-        <v>19200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>18400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>17600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>17100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>14200</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>16800</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E33" s="3">
         <v>22100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V33" s="3">
         <v>8900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E35" s="3">
         <v>22100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V35" s="3">
         <v>8900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,56 +2744,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>62100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>136100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>162200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>155000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>135300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,56 +2884,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E43" s="3">
         <v>28000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20800</v>
       </c>
-      <c r="H43" s="3">
-        <v>24500</v>
-      </c>
       <c r="I43" s="3">
+        <v>23500</v>
+      </c>
+      <c r="J43" s="3">
         <v>15000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2862,56 +2955,59 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E44" s="3">
         <v>5900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7600</v>
       </c>
-      <c r="F44" s="3">
-        <v>9000</v>
-      </c>
       <c r="G44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="H44" s="3">
         <v>9200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7800</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2930,56 +3026,59 @@
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>11300</v>
+      </c>
+      <c r="M45" s="3">
+        <v>14400</v>
+      </c>
+      <c r="N45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="P45" s="3">
         <v>13200</v>
       </c>
-      <c r="E45" s="3">
-        <v>10200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>11900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>13100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>11300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>14400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>13200</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2998,56 +3097,59 @@
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E46" s="3">
         <v>50700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>52700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>105300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>181500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>104000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>112500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>190000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>181400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>157100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3066,31 +3168,34 @@
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3134,56 +3239,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1728800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1661000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1609800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1558700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1490500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1409500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1373200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1337600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1277800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1249000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1204600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1191000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>975700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>953200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3202,56 +3310,59 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1247900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1249100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1250800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1252400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1254800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1230400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1231900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1233400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1232900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1228100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1188800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1190000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>884300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>881200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>862600</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,56 +3523,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E52" s="3">
         <v>12400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12000</v>
       </c>
-      <c r="F52" s="3">
-        <v>9600</v>
-      </c>
       <c r="G52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H52" s="3">
         <v>9000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,56 +3665,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3045900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2973100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2925300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2881500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2859700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2830600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2717300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2686200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2631500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2561000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2502900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2448100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2079600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2043500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1977600</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,56 +3792,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E57" s="3">
         <v>40100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>36100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3730,34 +3861,37 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10000</v>
+        <v>57300</v>
       </c>
       <c r="E58" s="3">
-        <v>7700</v>
+        <v>56100</v>
       </c>
       <c r="F58" s="3">
+        <v>52500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>44700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>43600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>42700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>42000</v>
+      </c>
+      <c r="K58" s="3">
         <v>700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>600</v>
@@ -3769,7 +3903,7 @@
         <v>600</v>
       </c>
       <c r="O58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="P58" s="3">
         <v>8900</v>
@@ -3777,8 +3911,8 @@
       <c r="Q58" s="3">
         <v>8900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="R58" s="3">
+        <v>8900</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
@@ -3798,56 +3932,59 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>129800</v>
+        <v>46800</v>
       </c>
       <c r="E59" s="3">
-        <v>133300</v>
+        <v>45200</v>
       </c>
       <c r="F59" s="3">
-        <v>135200</v>
+        <v>45800</v>
       </c>
       <c r="G59" s="3">
-        <v>139400</v>
+        <v>55500</v>
       </c>
       <c r="H59" s="3">
-        <v>150300</v>
+        <v>60900</v>
       </c>
       <c r="I59" s="3">
-        <v>122600</v>
+        <v>71900</v>
       </c>
       <c r="J59" s="3">
+        <v>43600</v>
+      </c>
+      <c r="K59" s="3">
         <v>128200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>113600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>109700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>107200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>102300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>101200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>105200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3866,56 +4003,59 @@
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>193700</v>
+      </c>
+      <c r="E60" s="3">
         <v>180000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>169600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>174900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>187100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>153600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>141800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>135900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>141700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>130200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>136800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>138300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>121900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3934,56 +4074,59 @@
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>932900</v>
+        <v>1770700</v>
       </c>
       <c r="E61" s="3">
-        <v>927200</v>
+        <v>1747800</v>
       </c>
       <c r="F61" s="3">
-        <v>911500</v>
+        <v>1738000</v>
       </c>
       <c r="G61" s="3">
-        <v>911300</v>
+        <v>1720900</v>
       </c>
       <c r="H61" s="3">
-        <v>911000</v>
+        <v>1717700</v>
       </c>
       <c r="I61" s="3">
-        <v>910800</v>
+        <v>1707200</v>
       </c>
       <c r="J61" s="3">
+        <v>1669600</v>
+      </c>
+      <c r="K61" s="3">
         <v>910600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>910400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>910200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>909800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>911700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>617200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>619300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1068800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4002,56 +4145,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>910900</v>
+        <v>4600</v>
       </c>
       <c r="E62" s="3">
-        <v>894700</v>
+        <v>4500</v>
       </c>
       <c r="F62" s="3">
-        <v>885500</v>
+        <v>4400</v>
       </c>
       <c r="G62" s="3">
-        <v>880800</v>
+        <v>4400</v>
       </c>
       <c r="H62" s="3">
-        <v>867100</v>
+        <v>6000</v>
       </c>
       <c r="I62" s="3">
-        <v>824200</v>
+        <v>6300</v>
       </c>
       <c r="J62" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K62" s="3">
         <v>820000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>803700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>767500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>750000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>749000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>717300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>711900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>745200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,56 +4429,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2066500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2023700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1996500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1966500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1967000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1965200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1888600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1885100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1855900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1813600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1801500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1791000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1471400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1469500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1936000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E72" s="3">
         <v>133300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>111200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>94600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>82200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>62700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>35600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-62900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-98400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-134700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-162100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-51800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,56 +5095,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>979400</v>
+      </c>
+      <c r="E76" s="3">
         <v>949400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>928700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>915000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>892700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>865400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>828700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>801100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>775600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>747400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>701400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>657200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>608200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>574000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E81" s="3">
         <v>22100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V81" s="3">
         <v>8900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,56 +5413,57 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>20300</v>
+        <v>15900</v>
       </c>
       <c r="E83" s="3">
-        <v>19600</v>
+        <v>14800</v>
       </c>
       <c r="F83" s="3">
-        <v>18600</v>
+        <v>15600</v>
       </c>
       <c r="G83" s="3">
-        <v>17600</v>
+        <v>13500</v>
       </c>
       <c r="H83" s="3">
-        <v>16500</v>
+        <v>13600</v>
       </c>
       <c r="I83" s="3">
-        <v>17300</v>
+        <v>13400</v>
       </c>
       <c r="J83" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K83" s="3">
         <v>16300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,56 +5837,59 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E89" s="3">
         <v>60900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>58000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>39200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>48400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>50100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>67000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>43700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>50800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>53100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>81500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>33600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,56 +5937,57 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-81800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-109400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-90800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-72100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-46400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,56 +6148,59 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-67700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-85700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-123400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-63200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-56300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-89800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-453400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-28700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,31 +6248,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,56 +6530,59 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>290700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
@@ -6355,31 +6601,34 @@
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6423,56 +6672,59 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-74000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>37200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-32700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-142600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>20500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>4</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,212 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>251200</v>
+      </c>
+      <c r="E8" s="3">
         <v>249300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>255000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>239200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>230100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>234100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>236900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>226000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>214400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>217600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>225200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>219400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>191500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>194300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>197100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>175500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>162000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>155800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>101900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>155300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>158300</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>165600</v>
+      </c>
+      <c r="E9" s="3">
         <v>172700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>169500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>161200</v>
       </c>
-      <c r="G9" s="3">
-        <v>167100</v>
-      </c>
       <c r="H9" s="3">
+        <v>149000</v>
+      </c>
+      <c r="I9" s="3">
         <v>160300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>159000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>149600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -904,35 +910,38 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E10" s="3">
         <v>76700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>85600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78000</v>
       </c>
-      <c r="G10" s="3">
-        <v>63000</v>
-      </c>
       <c r="H10" s="3">
+        <v>81200</v>
+      </c>
+      <c r="I10" s="3">
         <v>73800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>76400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -975,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,59 +1160,62 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>100</v>
       </c>
       <c r="L14" s="3">
         <v>100</v>
       </c>
       <c r="M14" s="3">
+        <v>100</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>3300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1204,46 +1223,49 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E15" s="3">
         <v>21200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>206400</v>
+      </c>
+      <c r="E17" s="3">
         <v>201700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>197100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>198200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>189700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>189500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>189000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>180400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>175800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>174700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>170800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>167500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>144500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>154800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>338200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>128600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W17" s="3">
         <v>131300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E18" s="3">
         <v>47700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>44600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>47900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>45500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>42900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>54400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>51900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>39500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-141100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>24000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,23 +1511,24 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
         <v>-5200</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1505,150 +1538,156 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-14200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>-16800</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E21" s="3">
         <v>68900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>78200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>59000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>62200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>64400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>62800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>59400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-142300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45300</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>18200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E22" s="3">
         <v>20700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>20000</v>
       </c>
       <c r="G22" s="3">
         <v>20000</v>
       </c>
       <c r="H22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I22" s="3">
         <v>19100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>700</v>
       </c>
       <c r="L22" s="3">
         <v>700</v>
@@ -1660,182 +1699,191 @@
         <v>700</v>
       </c>
       <c r="O22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>500</v>
       </c>
       <c r="Q22" s="3">
+        <v>500</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E23" s="3">
         <v>28900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>34300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>43800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-154900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W23" s="3">
         <v>6800</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>6600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>4500</v>
       </c>
       <c r="H24" s="3">
         <v>4500</v>
       </c>
       <c r="I24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J24" s="3">
         <v>7200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-44600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>22300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-110300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>24600</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W26" s="3">
         <v>8900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>22300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>27100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-110300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24600</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W27" s="3">
         <v>8900</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,23 +2397,26 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
         <v>5200</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2357,124 +2426,130 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>14200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>16800</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>22300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-110300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24600</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W33" s="3">
         <v>8900</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>22300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-110300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24600</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W35" s="3">
         <v>8900</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,59 +2830,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E41" s="3">
         <v>16500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>62100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>136100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>74900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>162200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>155000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>135300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2816,8 +2902,11 @@
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,59 +2976,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E43" s="3">
         <v>18300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2958,59 +3050,62 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E44" s="3">
         <v>5500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7800</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3029,59 +3124,62 @@
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>5000</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G45" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3100,59 +3198,62 @@
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E46" s="3">
         <v>52800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>60900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>105300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>104000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>112500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>101200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>58800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>190000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>181400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>157100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3171,8 +3272,11 @@
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3197,8 +3301,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3242,59 +3346,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1739500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1728800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1661000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1609800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1558700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1490500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1409500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1373200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1337600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1277800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1249000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1204600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1191000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>975700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>953200</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3313,59 +3420,62 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1247200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1247900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1249100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1250800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1252400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1254800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1230400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1231900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1233400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1232900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1228100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1188800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1190000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>884300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>881200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>862600</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,59 +3642,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E52" s="3">
         <v>16500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,59 +3790,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3101800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3045900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2973100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2925300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2881500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2859700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2830600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2717300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2686200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2631500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2561000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2502900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2448100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2079600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2043500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1977600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3739,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,59 +3922,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E57" s="3">
         <v>44700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>40100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3864,37 +3994,40 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E58" s="3">
         <v>57300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>52500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>42000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>600</v>
       </c>
       <c r="M58" s="3">
         <v>600</v>
@@ -3906,7 +4039,7 @@
         <v>600</v>
       </c>
       <c r="P58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q58" s="3">
         <v>8900</v>
@@ -3914,8 +4047,8 @@
       <c r="R58" s="3">
         <v>8900</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="S58" s="3">
+        <v>8900</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
@@ -3935,59 +4068,62 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E59" s="3">
         <v>46800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>60900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>71900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>128200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>113600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>109700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>107200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>102300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>101200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>105200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>95700</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4006,59 +4142,62 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E60" s="3">
         <v>193700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>180000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>169600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>187100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>153600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>154500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>141800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>135900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>141700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>130200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>136800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>138300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>121900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4077,59 +4216,62 @@
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1813000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1770700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1747800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1738000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1720900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1717700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1707200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1669600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>910600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>910400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>910200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>909800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>911700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>617200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>619300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1068800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4148,59 +4290,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>4600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>4400</v>
       </c>
       <c r="G62" s="3">
         <v>4400</v>
       </c>
       <c r="H62" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I62" s="3">
         <v>6000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>820000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>803700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>767500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>750000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>749000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>717300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>711900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>745200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,59 +4586,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2103400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2066500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2023700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1996500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1966500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1967000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1965200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1888600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1885100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1855900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1813600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1801500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1791000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1471400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1469500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1936000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4503,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4984,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E72" s="3">
         <v>155700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>133300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>111200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>94600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>82200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>62700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>35600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-27300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-62900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-98400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-134700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-162100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-51800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4885,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,59 +5280,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>998400</v>
+      </c>
+      <c r="E76" s="3">
         <v>979400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>949400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>928700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>915000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>892700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>865400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>828700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>801100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>775600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>747400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>701400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>657200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>608200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>574000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5169,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>22300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-110300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24600</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W81" s="3">
         <v>8900</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,59 +5611,60 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E83" s="3">
         <v>15900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,59 +6053,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E89" s="3">
         <v>80000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>60900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>58000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>39200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>48400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>67000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>43700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>50800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>53100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>81500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>33600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
       </c>
@@ -5911,8 +6127,11 @@
       <c r="Y89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,59 +6157,60 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-96800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-81300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-81800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-109400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-90800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-72100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-55600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-32300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6009,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,59 +6377,62 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-78800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-67700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-76900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-85700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-123400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>12900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-63200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-89800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-453400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
@@ -6222,8 +6451,11 @@
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6275,8 +6508,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,59 +6775,62 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E100" s="3">
         <v>11700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>290700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
@@ -6604,8 +6849,11 @@
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6630,8 +6878,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6675,59 +6923,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-74000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>37200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-32700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>50600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-142600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20500</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
       </c>
@@ -6744,6 +6995,9 @@
         <v>4</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,221 +656,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>261700</v>
+      </c>
+      <c r="E8" s="3">
         <v>251200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>249300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>255000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>239200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>230100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>234100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>236900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>226000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>214400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>217600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>225200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>219400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>191500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>194300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>197100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>175500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>162000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>155800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>101900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>155300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>158300</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>176000</v>
+      </c>
+      <c r="E9" s="3">
         <v>165600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>172700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>169500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>161200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>149000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>160300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>159000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>149600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,29 +932,29 @@
         <v>85600</v>
       </c>
       <c r="E10" s="3">
+        <v>85600</v>
+      </c>
+      <c r="F10" s="3">
         <v>76700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>85600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>81200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>73800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,62 +1180,65 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>13100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>100</v>
       </c>
       <c r="M14" s="3">
         <v>100</v>
       </c>
       <c r="N14" s="3">
+        <v>100</v>
+      </c>
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>3300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1226,49 +1246,52 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E15" s="3">
         <v>20300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>208600</v>
+      </c>
+      <c r="E17" s="3">
         <v>206400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>201700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>197100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>198200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>189700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>189500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>189000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>180400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>175800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>174700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>170800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>167500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>144500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>154800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>338200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>128600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X17" s="3">
         <v>131300</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E18" s="3">
         <v>44800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>41000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>44600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>47900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>38600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>42900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>54400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>51900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>47000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>39500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-141100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>46900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>24000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,26 +1545,27 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
         <v>-5200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1541,156 +1575,162 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-14200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-16800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E21" s="3">
         <v>65100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>68900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>78200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>65800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>59000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>62200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>64400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>62800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>48700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>59400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>55500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-142300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>45300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>18200</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="3">
         <v>18600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>20000</v>
       </c>
       <c r="H22" s="3">
         <v>20000</v>
       </c>
       <c r="I22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="J22" s="3">
         <v>19100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
@@ -1702,188 +1742,197 @@
         <v>700</v>
       </c>
       <c r="P22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="Q22" s="3">
         <v>500</v>
       </c>
       <c r="R22" s="3">
+        <v>500</v>
+      </c>
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E23" s="3">
         <v>13200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>43800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-154900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X23" s="3">
         <v>6800</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E24" s="3">
         <v>4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>4500</v>
       </c>
       <c r="I24" s="3">
         <v>4500</v>
       </c>
       <c r="J24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K24" s="3">
         <v>7200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-44600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E26" s="3">
         <v>9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-110300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="3">
         <v>8900</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-110300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="3">
         <v>8900</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,26 +2467,29 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
         <v>5200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2429,127 +2499,133 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>14200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>16800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-110300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X33" s="3">
         <v>8900</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-110300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="3">
         <v>8900</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,62 +2917,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E41" s="3">
         <v>67500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>69900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>37700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>162200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>155000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>135300</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2905,8 +2992,11 @@
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,62 +3069,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E43" s="3">
         <v>13500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3053,62 +3146,65 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E44" s="3">
         <v>10500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7800</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3127,62 +3223,65 @@
       <c r="Z44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E45" s="3">
         <v>5000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3201,62 +3300,65 @@
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E46" s="3">
         <v>99100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>52800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>60900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>105300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>181500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>104000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>112500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>75800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>101200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>58800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>190000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>181400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>157100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3304,8 +3409,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3349,62 +3454,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1762300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1739500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1728800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1661000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1609800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1558700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1490500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1409500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1373200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1337600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1277800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1249000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1204600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1191000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1000000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>975700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>953200</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3423,62 +3531,65 @@
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1246800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1247200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1247900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1249100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1250800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1252400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1254800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1230400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1231900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1233400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1232900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1228100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1188800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1190000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>884300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>881200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>862600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,62 +3762,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E52" s="3">
         <v>9700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,62 +3916,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3090600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3101800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3045900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2973100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2925300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2881500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2859700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2830600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2717300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2686200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2631500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2561000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2502900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2448100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2079600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2043500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1977600</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,62 +4053,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E57" s="3">
         <v>30000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>36100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>24200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3997,40 +4128,43 @@
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E58" s="3">
         <v>56700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>57300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>56100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>52500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>43600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>42700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>600</v>
@@ -4042,7 +4176,7 @@
         <v>600</v>
       </c>
       <c r="Q58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="R58" s="3">
         <v>8900</v>
@@ -4050,8 +4184,8 @@
       <c r="S58" s="3">
         <v>8900</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
+      <c r="T58" s="3">
+        <v>8900</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
@@ -4071,62 +4205,65 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E59" s="3">
         <v>54000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>46800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>45800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>55500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>60900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>71900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>113600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>109700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>107200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>102300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>101200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>105200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>95700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4145,62 +4282,65 @@
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E60" s="3">
         <v>187000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>193700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>180000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>174700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>169600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>174900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>187100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>153600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>154500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>141800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>135900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>141700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>130200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>136800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>138300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>121900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,62 +4359,65 @@
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1751700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1813000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1770700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1747800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1738000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1720900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1717700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1707200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1669600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>910600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>910400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>910200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>909800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>911700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>617200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>619300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1068800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4293,62 +4436,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>4400</v>
       </c>
       <c r="H62" s="3">
         <v>4400</v>
       </c>
       <c r="I62" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J62" s="3">
         <v>6000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>820000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>803700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>767500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>750000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>749000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>717300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>711900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>745200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,62 +4744,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2056700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2103400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2066500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2023700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1996500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1966500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1967000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1965200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1888600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1885100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1855900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1813600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1801500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1791000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1471400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1469500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1936000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,62 +5158,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>191800</v>
+      </c>
+      <c r="E72" s="3">
         <v>164800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>155700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>133300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>111200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>94600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>82200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>62700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>35600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-62900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-98400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-134700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-162100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-51800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,62 +5466,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1033900</v>
+      </c>
+      <c r="E76" s="3">
         <v>998400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>979400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>949400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>928700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>915000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>892700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>865400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>828700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>801100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>775600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>747400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>701400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>657200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>608200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>574000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-110300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X81" s="3">
         <v>8900</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,62 +5810,63 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E83" s="3">
         <v>16900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,62 +6270,65 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E89" s="3">
         <v>49800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>80000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>60900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>58000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>48400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>50100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>67000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>43700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>50800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>53100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>81500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>33600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,62 +6378,63 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-70200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-96800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-81300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-109400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-90800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-72100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-46400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,62 +6607,65 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E94" s="3">
         <v>23600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-78800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-67700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-76900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-85700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-123400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-63200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-56300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-89800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-453400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-28700</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6511,8 +6745,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,62 +7021,65 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>290700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
@@ -6852,8 +7098,11 @@
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6881,8 +7130,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6926,62 +7175,65 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E102" s="3">
         <v>51000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-74000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>66300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-32700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>50600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-142600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>4</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,231 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>265400</v>
+      </c>
+      <c r="E8" s="3">
         <v>261700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>251200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>249300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>255000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>239200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>230100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>234100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>236900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>226000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>214400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>217600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>225200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>219400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>191500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>194300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>197100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>175500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>162000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>155800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>101900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>155300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>158300</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>182500</v>
+      </c>
+      <c r="E9" s="3">
         <v>176000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>165600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>172700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>169500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>161200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>149000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>160300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>159000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>149600</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
@@ -923,41 +930,44 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>85600</v>
+        <v>83000</v>
       </c>
       <c r="E10" s="3">
         <v>85600</v>
       </c>
       <c r="F10" s="3">
+        <v>85600</v>
+      </c>
+      <c r="G10" s="3">
         <v>76700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>85600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>78000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>81200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>77800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>76400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,65 +1200,68 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
-      </c>
-      <c r="M14" s="3">
-        <v>100</v>
       </c>
       <c r="N14" s="3">
         <v>100</v>
       </c>
       <c r="O14" s="3">
+        <v>100</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>3300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1249,52 +1269,55 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E15" s="3">
         <v>20900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17300</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E17" s="3">
         <v>208600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>206400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>201700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>197100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>198200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>189700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>189500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>189000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>180400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>175800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>174700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>170800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>167500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>144500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>154800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>338200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>128600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="3">
         <v>131300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E18" s="3">
         <v>53100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>44800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>41000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>40500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>44600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>42900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>54400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>51900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-141100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>24000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,29 +1579,30 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
         <v>-5200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1578,162 +1612,168 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-14200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-13300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-16800</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E21" s="3">
         <v>74000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>65100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>68900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>78200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>65800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>59000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>62200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>64400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>62800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>48700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>59400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>47300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-142300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>45300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>18200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>20000</v>
       </c>
       <c r="I22" s="3">
         <v>20000</v>
       </c>
       <c r="J22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K22" s="3">
         <v>19100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
@@ -1745,194 +1785,203 @@
         <v>700</v>
       </c>
       <c r="Q22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>500</v>
       </c>
       <c r="S22" s="3">
+        <v>500</v>
+      </c>
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E23" s="3">
         <v>36900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>27800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>32800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>43800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>41000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-154900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y23" s="3">
         <v>6800</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E24" s="3">
         <v>9900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>4500</v>
       </c>
       <c r="J24" s="3">
         <v>4500</v>
       </c>
       <c r="K24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="L24" s="3">
         <v>7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-44600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E26" s="3">
         <v>27000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-110300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24600</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="3">
         <v>8900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E27" s="3">
         <v>27000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-110300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24600</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="3">
         <v>8900</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,29 +2537,32 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
         <v>5200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2502,130 +2572,136 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>14200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>13300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>16800</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E33" s="3">
         <v>27000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-110300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24600</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="3">
         <v>8900</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E35" s="3">
         <v>27000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-110300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24600</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="3">
         <v>8900</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,65 +3004,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E41" s="3">
         <v>39100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>62100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>136100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>69900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>162200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>155000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>135300</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2995,8 +3082,11 @@
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,65 +3162,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E43" s="3">
         <v>11800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3149,65 +3242,68 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E44" s="3">
         <v>10000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>15500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7800</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3226,65 +3322,68 @@
       <c r="AA44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3303,65 +3402,68 @@
       <c r="AA45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E46" s="3">
         <v>65700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>99100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>52700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>60900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>105300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>104000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>112500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>75800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>101200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>58800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>190000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>181400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>157100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3412,8 +3517,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3457,65 +3562,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1785800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1762300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1739500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1728800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1661000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1609800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1558700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1490500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1409500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1373200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1337600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1277800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1249000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1204600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1191000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>975700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>953200</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3534,65 +3642,68 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1246300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1246800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1247200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1247900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1249100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1250800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1252400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1254800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1230400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1231900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1233400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1232900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1228100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1188800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1190000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>884300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>881200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>862600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,65 +3882,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9800</v>
+        <v>16300</v>
       </c>
       <c r="E52" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F52" s="3">
         <v>9700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4700</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,65 +4042,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3106000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3090600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3101800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3045900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2973100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2925300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2881500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2859700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2830600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2717300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2686200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2631500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2561000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2502900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2448100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2079600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2043500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1977600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,65 +4184,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E57" s="3">
         <v>36200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4131,43 +4262,46 @@
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E58" s="3">
         <v>50900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>57300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>56100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>43600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>42000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>600</v>
       </c>
       <c r="O58" s="3">
         <v>600</v>
@@ -4179,7 +4313,7 @@
         <v>600</v>
       </c>
       <c r="R58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="S58" s="3">
         <v>8900</v>
@@ -4187,8 +4321,8 @@
       <c r="T58" s="3">
         <v>8900</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>8900</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -4208,65 +4342,68 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E59" s="3">
         <v>50500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>54000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>45200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>45800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>113600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>109700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>107200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>102300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>101200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>105200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>95700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4285,65 +4422,68 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E60" s="3">
         <v>193600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>187000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>193700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>180000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>169600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>174900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>187100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>153600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>154500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>141800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>135900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>141700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>130200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>136800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>138300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>121900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4362,65 +4502,68 @@
       <c r="AA60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1737300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1751700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1813000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1770700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1747800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1738000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1720900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1717700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1707200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1669600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>910600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>910400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>910200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>909800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>911700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>617200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>619300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1068800</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4439,65 +4582,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4400</v>
       </c>
       <c r="I62" s="3">
         <v>4400</v>
       </c>
       <c r="J62" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K62" s="3">
         <v>6000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>820000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>803700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>767500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>750000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>749000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>717300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>711900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>745200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,65 +4902,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2056700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2103400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2066500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2023700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1996500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1966500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1967000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1965200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1888600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1885100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1855900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1813600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1801500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1791000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1471400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1469500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1936000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,65 +5332,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>220400</v>
+      </c>
+      <c r="E72" s="3">
         <v>191800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>164800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>155700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>133300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>111200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>94600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>82200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>62700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>35600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-62900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-98400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-134700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-162100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-51800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,65 +5652,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1071000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1033900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>998400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>979400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>949400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>928700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>915000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>892700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>865400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>828700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>801100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>775600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>747400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>701400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>657200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>608200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>574000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>41600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E81" s="3">
         <v>27000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-110300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24600</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y81" s="3">
         <v>8900</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,65 +6009,66 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E83" s="3">
         <v>18000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,65 +6487,68 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E89" s="3">
         <v>87600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>49800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>80000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>60900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>58000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>48400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>50100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>67000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>50800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>53100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>81500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>33600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,65 +6599,66 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-55100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-70200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-81800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-109400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-90800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-72100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-46400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,65 +6837,68 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>23600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-78800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-67700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-76900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-85700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-123400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-63200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-56300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-89800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-453400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-28700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6748,8 +6982,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,65 +7267,68 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-60900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>10700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>290700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7133,8 +7382,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7178,65 +7427,68 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>51000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-74000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>66300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-32700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>50600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-142600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>20500</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>4</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>MCW</t>
   </si>
@@ -656,251 +656,257 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>261200</v>
+      </c>
+      <c r="E8" s="3">
         <v>263400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>265400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>261700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>251200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>249300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>255000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>239200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>230100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>234100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>236900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>226000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>214400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>217600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>225200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>219400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>191500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>194300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>197100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>175500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>162000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>155800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>101900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>155300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>158300</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>168400</v>
+      </c>
+      <c r="E9" s="3">
         <v>183100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>182500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>176000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>165600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>172700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>169500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>161200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>149000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>160300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>159000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>149600</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
@@ -943,47 +949,50 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E10" s="3">
         <v>80300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>85600</v>
       </c>
       <c r="G10" s="3">
         <v>85600</v>
       </c>
       <c r="H10" s="3">
+        <v>85600</v>
+      </c>
+      <c r="I10" s="3">
         <v>76700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>85600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>81200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>76400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1026,8 +1035,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,71 +1239,74 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E14" s="3">
         <v>2800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>13100</v>
-      </c>
       <c r="H14" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
-      </c>
-      <c r="O14" s="3">
-        <v>100</v>
       </c>
       <c r="P14" s="3">
         <v>100</v>
       </c>
       <c r="Q14" s="3">
+        <v>100</v>
+      </c>
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>3300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1295,58 +1314,61 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>2000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E15" s="3">
         <v>22400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>17300</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1389,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>208700</v>
+      </c>
+      <c r="E17" s="3">
         <v>208800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>210600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>208600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>206400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>201700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>197100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>198200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>189700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>189500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>189000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>180400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>175800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>174700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>170800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>167500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>144500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>154800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>338200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>128600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="3">
         <v>131300</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E18" s="3">
         <v>54600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>54800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>44800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>57900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>41000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>44600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>54400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>51900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>39500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-141100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>46900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>24000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,35 +1646,36 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>5200</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1652,174 +1685,180 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-14200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-16800</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>75700</v>
+      </c>
+      <c r="E21" s="3">
         <v>77000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>76600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>74000</v>
       </c>
-      <c r="G21" s="3">
-        <v>65100</v>
-      </c>
       <c r="H21" s="3">
+        <v>59900</v>
+      </c>
+      <c r="I21" s="3">
         <v>68900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>78200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>65800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>59000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>62200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>64400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>62800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>40700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>48700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>59400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>55500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>47300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-142300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>18200</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E22" s="3">
         <v>14100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>20000</v>
       </c>
       <c r="K22" s="3">
         <v>20000</v>
       </c>
       <c r="L22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M22" s="3">
         <v>19100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
@@ -1831,206 +1870,215 @@
         <v>700</v>
       </c>
       <c r="S22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="T22" s="3">
         <v>500</v>
       </c>
       <c r="U22" s="3">
+        <v>500</v>
+      </c>
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E23" s="3">
         <v>37800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>34700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>23700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>45600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>43800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>41000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-154900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="3">
         <v>6800</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>10400</v>
+        <v>7000</v>
       </c>
       <c r="E24" s="3">
         <v>10400</v>
       </c>
       <c r="F24" s="3">
+        <v>10400</v>
+      </c>
+      <c r="G24" s="3">
         <v>9900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>4500</v>
       </c>
       <c r="L24" s="3">
         <v>4500</v>
       </c>
       <c r="M24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N24" s="3">
         <v>7200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-44600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E26" s="3">
         <v>27400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>35700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-110300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24600</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="3">
         <v>8900</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E27" s="3">
         <v>27400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>28600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>36300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-110300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24600</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA27" s="3">
         <v>8900</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,35 +2676,38 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-5200</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>5200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2648,136 +2717,142 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>14200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="3">
         <v>16800</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E33" s="3">
         <v>27400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>28600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>36300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-110300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24600</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA33" s="3">
         <v>8900</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E35" s="3">
         <v>27400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>28600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>36300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-110300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24600</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA35" s="3">
         <v>8900</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,71 +3177,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E41" s="3">
         <v>35700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>67500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>136100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>69900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>65200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>37700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>70300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>162200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>155000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>135300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3175,8 +3261,11 @@
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,71 +3347,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E43" s="3">
         <v>17100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3341,71 +3433,74 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E44" s="3">
         <v>9300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3424,71 +3519,74 @@
       <c r="AC44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3507,71 +3605,74 @@
       <c r="AC45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E46" s="3">
         <v>68800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>65700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>99100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>52800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>105300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>104000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>106100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>112500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>75800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>101200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>58800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>190000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>181400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>157100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3590,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3628,8 +3732,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3673,71 +3777,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1856700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1817100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1785800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1762300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1739500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1728800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1661000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1609800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1558700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1490500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1409500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1373200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1337600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1277800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1249000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1204600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1191000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1000000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>975700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>953200</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3756,71 +3863,74 @@
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1245700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1245900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1246300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1246800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1247200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1247900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1249100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1250800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1252400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1254800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1230400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1231900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1233400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1232900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1228100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1188800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1190000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>884300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>881200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>862600</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3839,8 +3949,11 @@
       <c r="AC49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,71 +4121,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E52" s="3">
         <v>11200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4088,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,71 +4293,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3173100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3142900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3106000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3090600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3101800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3045900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2973100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2925300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2881500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2859700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2830600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2717300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2686200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2631500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2561000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2502900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2448100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2079600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2043500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1977600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4254,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,71 +4445,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E57" s="3">
         <v>36100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>40100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4399,49 +4529,52 @@
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E58" s="3">
         <v>53200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>51900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>56700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>57300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>56100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>52500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>600</v>
       </c>
       <c r="Q58" s="3">
         <v>600</v>
@@ -4453,7 +4586,7 @@
         <v>600</v>
       </c>
       <c r="T58" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="U58" s="3">
         <v>8900</v>
@@ -4461,8 +4594,8 @@
       <c r="V58" s="3">
         <v>8900</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="W58" s="3">
+        <v>8900</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
@@ -4482,71 +4615,74 @@
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E59" s="3">
         <v>55400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>50500</v>
       </c>
-      <c r="G59" s="3">
-        <v>54000</v>
-      </c>
       <c r="H59" s="3">
+        <v>55100</v>
+      </c>
+      <c r="I59" s="3">
         <v>46800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>60900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>71900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>113600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>109700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>107200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>102300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>101200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>105200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>95700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4565,71 +4701,74 @@
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>184800</v>
+      </c>
+      <c r="E60" s="3">
         <v>193700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>176400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>193600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>187000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>193700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>180000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>174700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>169600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>174900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>187100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>153600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>154500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>141800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>135900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>141700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>130200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>136800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>138300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>121900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4648,71 +4787,74 @@
       <c r="AC60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1715900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1711100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1737300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1751700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1813000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1770700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1747800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1738000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1720900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1717700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1707200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1669600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>910600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>910400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>910200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>909800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>911700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>617200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>619300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1068800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4731,71 +4873,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>4400</v>
       </c>
       <c r="K62" s="3">
         <v>4400</v>
       </c>
       <c r="L62" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M62" s="3">
         <v>6000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>820000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>803700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>767500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>750000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>749000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>717300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>711900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>745200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4814,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,71 +5217,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2040100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2037800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2035000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2056700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2103400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2066500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2023700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1996500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1966500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1967000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1965200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1888600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1885100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1855900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1813600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1801500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1791000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1471400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1469500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1936000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5146,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,71 +5679,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>267900</v>
+      </c>
+      <c r="E72" s="3">
         <v>247900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>220400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>191800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>164800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>155700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>133300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>111200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>94600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>82200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>62700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>35600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-62900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-98400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-134700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-162100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-51800</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5592,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,71 +6023,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1133000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1105200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1071000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1033900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>998400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>979400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>949400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>928700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>915000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>892700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>865400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>828700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>801100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>775600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>747400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>701400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>657200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>608200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>574000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>41600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5924,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E81" s="3">
         <v>27400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>28600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>36300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-110300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24600</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA81" s="3">
         <v>8900</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,71 +6406,72 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E83" s="3">
         <v>19900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>15100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
@@ -6292,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,71 +6920,74 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E89" s="3">
         <v>91400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>87600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>49800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>80000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>58000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>48400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>50100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>67000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>50800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>53100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>81500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>33600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>68100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>51600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
@@ -6790,8 +7006,11 @@
       <c r="AC89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,71 +7040,72 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-76700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-70200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-96800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-81300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-81800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-109400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-90800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-72100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-30000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-39400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-32300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6904,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,71 +7296,74 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-60500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-56400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-55000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>23600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-78800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-67700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-85700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-123400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-56300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-89800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-453400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28700</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
@@ -7153,8 +7382,11 @@
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7222,8 +7455,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7267,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,71 +7758,74 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-60900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>290700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
@@ -7599,8 +7844,11 @@
       <c r="AC100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7637,8 +7885,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7682,71 +7930,74 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E102" s="3">
         <v>9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>51000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>66300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>37200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-32700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>50600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-142600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20500</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
@@ -7763,6 +8014,9 @@
         <v>4</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
